--- a/content/tz-vk/tz-vk-tradicii-i-prazdniki-kitaya.xlsx
+++ b/content/tz-vk/tz-vk-tradicii-i-prazdniki-kitaya.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -593,25 +593,37 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Картинки</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТЕЛЬНО: обложка + 3 инфографики. Где нужно — несколько картинок. Мотив обложки: иероглиф 春节 «Праздник весны». Инфографики: Пять главных праздников; Традиции Нового года; Еда со смыслом. Подробно — лист «8. Картинки и проверка».</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Отстройка</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Показываем, что за красными фонарями — простая сердцевина: семья, память, пожелание добра. С иероглифами и легендами.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Объём</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>6 000–8 000 знаков (лонгрид) + 3 инфографики</t>
         </is>
@@ -755,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -817,37 +829,49 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1">
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Инфографики</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТЕЛЬНО 3 шт. (где нужно — несколько): Пять главных праздников: 春节/元宵节/清明节/端午节/中秋节 — карточки с пиньинем и «чем известен».; Традиции Нового года: 红包, 春联, фейерверки, 团圆饭 — 4 плашки.; Еда со смыслом: 饺子, 鱼, 月饼, 粽子, 汤圆, 年糕 — что означает каждое блюдо.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Хэштеги</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>#китай #традициикитая #праздникикитая #китайскийновыйгод #春节 #культуракитая #праздникфонарей #中国</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Формат публикации</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>«Статья ВК» + карточки праздников/еды.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Ссылки / CTA</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Верх воронки (ст. 0–1) — без офферов. Мягкая ссылка на школу допустима у ст. 2–4, в конце, ненавязчиво.</t>
         </is>
